--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="298">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -922,6 +922,10 @@
   </si>
   <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -4988,10 +4992,10 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -4999,10 +5003,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5028,14 +5032,14 @@
         <v>287</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5084,22 +5088,22 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$46</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="358">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -553,16 +553,212 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>required</t>
+    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>RXR-1</t>
+  </si>
+  <si>
+    <t>Dosage.route.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
   </si>
   <si>
-    <t>.routeCode</t>
-  </si>
-  <si>
-    <t>RXR-1</t>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Dosage.route.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -614,16 +810,6 @@
     <t>Dosage.doseAndRate.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.type</t>
   </si>
   <si>
@@ -742,10 +928,6 @@
     <t>Dosage.doseAndRate.dose[x].comparator</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
@@ -758,6 +940,9 @@
     <t>If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>How the Quantity should be understood and represented.</t>
   </si>
   <si>
@@ -804,10 +989,6 @@
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x].system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
   </si>
   <si>
     <t>System that defines coded unit form</t>
@@ -1265,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL35"/>
+  <dimension ref="A1:AL46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.88671875" customWidth="true" bestFit="true"/>
@@ -1293,7 +1474,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1304,7 +1485,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3000,9 +3181,11 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
         <v>174</v>
       </c>
@@ -3043,7 +3226,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>177</v>
       </c>
@@ -3062,29 +3245,25 @@
         <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3108,13 +3287,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3132,7 +3311,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3144,52 +3323,54 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3226,19 +3407,19 @@
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3250,21 +3431,21 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3275,7 +3456,7 @@
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3284,19 +3465,23 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3344,44 +3529,44 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3393,17 +3578,15 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3440,31 +3623,31 @@
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>88</v>
@@ -3475,21 +3658,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3498,21 +3681,21 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3536,57 +3719,57 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3609,19 +3792,19 @@
         <v>104</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3631,7 +3814,7 @@
         <v>21</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>21</v>
@@ -3658,17 +3841,19 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3683,22 +3868,20 @@
         <v>80</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="C23" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3710,7 +3893,7 @@
         <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -3719,20 +3902,18 @@
         <v>104</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3780,7 +3961,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3795,22 +3976,20 @@
         <v>80</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>209</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3822,7 +4001,7 @@
         <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -3831,19 +4010,17 @@
         <v>104</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -3892,7 +4069,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3907,10 +4084,10 @@
         <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -3918,7 +4095,7 @@
         <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3938,19 +4115,21 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3998,7 +4177,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>87</v>
+        <v>222</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4010,32 +4189,32 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>88</v>
+        <v>223</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4044,21 +4223,23 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4094,45 +4275,45 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4155,19 +4336,19 @@
         <v>104</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4216,7 +4397,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4231,18 +4412,18 @@
         <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4253,36 +4434,36 @@
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>234</v>
+        <v>124</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q28" t="s" s="2">
-        <v>238</v>
-      </c>
+      <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4302,13 +4483,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4341,18 +4522,18 @@
         <v>80</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4366,7 +4547,7 @@
         <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4375,18 +4556,16 @@
         <v>104</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4410,11 +4589,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -4438,7 +4619,7 @@
         <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -4447,18 +4628,18 @@
         <v>80</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4478,21 +4659,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>84</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>85</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>257</v>
+        <v>86</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>258</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4540,7 +4719,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4549,35 +4728,35 @@
         <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>261</v>
+        <v>88</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -4586,23 +4765,21 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>180</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>181</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4638,45 +4815,45 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>96</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4699,19 +4876,17 @@
         <v>104</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>271</v>
+        <v>124</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -4736,13 +4911,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -4760,7 +4935,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4775,18 +4950,18 @@
         <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>277</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4809,19 +4984,19 @@
         <v>104</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -4858,19 +5033,17 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4885,20 +5058,22 @@
         <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
@@ -4910,7 +5085,7 @@
         <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -4919,19 +5094,19 @@
         <v>104</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -4980,7 +5155,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4992,23 +5167,25 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>293</v>
+        <v>248</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5020,7 +5197,7 @@
         <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5029,17 +5206,19 @@
         <v>104</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5088,29 +5267,1225 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AL35" t="s" s="2">
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q39" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="R39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Y40" s="2"/>
+      <c r="Z40" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL35">
+  <autoFilter ref="A1:AL46">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5120,7 +6495,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
+  <conditionalFormatting sqref="A2:AI45">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1229,7 +1229,7 @@
     <t>TODO</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]:doseQuantity.id</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -371,7 +371,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>Freitext-Dosierungsanweisung, wenn keine strukturierte Angabe möglich ist.</t>
+    <t>Textdarstellung der Dosierung: bei strukturierter Dosierung durch die Fachanwendung generiert, sonst Freitext-Dosierungsanweisung (wenn keine strukturierte Angabe möglich ist).</t>
   </si>
   <si>
     <t>Free text dosage instructions e.g. SIG.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -294,6 +294,9 @@
     <t>Dosage.extension</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -325,9 +328,6 @@
   </si>
   <si>
     <t>DosageCategory</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category}
@@ -2431,7 +2431,7 @@
         <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2440,13 +2440,13 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2485,19 +2485,19 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -2509,7 +2509,7 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -2520,13 +2520,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>21</v>
@@ -2539,7 +2539,7 @@
         <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>21</v>
@@ -2605,7 +2605,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2617,7 +2617,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2648,19 +2648,19 @@
         <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2723,7 +2723,7 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2751,13 +2751,13 @@
         <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
         <v>108</v>
@@ -2859,13 +2859,13 @@
         <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>85</v>
@@ -2967,13 +2967,13 @@
         <v>77</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>120</v>
@@ -3192,7 +3192,7 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>132</v>
@@ -3239,19 +3239,19 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3263,7 +3263,7 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>89</v>
@@ -3291,13 +3291,13 @@
         <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>136</v>
@@ -3516,7 +3516,7 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>132</v>
@@ -3563,19 +3563,19 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3587,7 +3587,7 @@
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>89</v>
@@ -3615,13 +3615,13 @@
         <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>147</v>
@@ -3725,13 +3725,13 @@
         <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>85</v>
@@ -3833,13 +3833,13 @@
         <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>163</v>
@@ -3941,13 +3941,13 @@
         <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>85</v>
@@ -4055,7 +4055,7 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>178</v>
@@ -4165,7 +4165,7 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>85</v>
@@ -4269,13 +4269,13 @@
         <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>85</v>
@@ -4375,13 +4375,13 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>198</v>
@@ -4485,13 +4485,13 @@
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>178</v>
@@ -4593,13 +4593,13 @@
         <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>120</v>
@@ -4818,7 +4818,7 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>132</v>
@@ -4865,19 +4865,19 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4889,7 +4889,7 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>89</v>
@@ -4917,13 +4917,13 @@
         <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>136</v>
@@ -5142,7 +5142,7 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>132</v>
@@ -5189,19 +5189,19 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5213,7 +5213,7 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>89</v>
@@ -5241,13 +5241,13 @@
         <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>147</v>
@@ -5351,13 +5351,13 @@
         <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>85</v>
@@ -5459,13 +5459,13 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>163</v>
@@ -5567,13 +5567,13 @@
         <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>85</v>
@@ -5681,7 +5681,7 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>178</v>
@@ -5791,7 +5791,7 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>85</v>
@@ -5895,13 +5895,13 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>120</v>
@@ -6118,7 +6118,7 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>132</v>
@@ -6165,19 +6165,19 @@
         <v>21</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6189,7 +6189,7 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>89</v>
@@ -6217,13 +6217,13 @@
         <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>136</v>
@@ -6442,7 +6442,7 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>132</v>
@@ -6489,19 +6489,19 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6513,7 +6513,7 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>89</v>
@@ -6541,13 +6541,13 @@
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>147</v>
@@ -6651,13 +6651,13 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>85</v>
@@ -6759,13 +6759,13 @@
         <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>163</v>
@@ -6867,13 +6867,13 @@
         <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>85</v>
@@ -6981,7 +6981,7 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>178</v>
@@ -7091,7 +7091,7 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>85</v>
@@ -7195,13 +7195,13 @@
         <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>120</v>
@@ -7420,7 +7420,7 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>132</v>
@@ -7467,19 +7467,19 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7491,7 +7491,7 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>89</v>
@@ -7519,13 +7519,13 @@
         <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>136</v>
@@ -7744,7 +7744,7 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>132</v>
@@ -7791,19 +7791,19 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7815,7 +7815,7 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>89</v>
@@ -7843,13 +7843,13 @@
         <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>147</v>
@@ -7953,13 +7953,13 @@
         <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>85</v>
@@ -8061,13 +8061,13 @@
         <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>163</v>
@@ -8169,13 +8169,13 @@
         <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>85</v>
@@ -8283,7 +8283,7 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>178</v>
@@ -8393,7 +8393,7 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>85</v>
@@ -8497,13 +8497,13 @@
         <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>271</v>
@@ -8718,7 +8718,7 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>132</v>
@@ -8765,19 +8765,19 @@
         <v>21</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8789,7 +8789,7 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>89</v>
@@ -8823,7 +8823,7 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>120</v>
@@ -8925,13 +8925,13 @@
         <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>285</v>
@@ -9035,13 +9035,13 @@
         <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>295</v>
@@ -9260,7 +9260,7 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>132</v>
@@ -9307,19 +9307,19 @@
         <v>21</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9331,7 +9331,7 @@
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>89</v>
@@ -9359,13 +9359,13 @@
         <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>303</v>
@@ -9582,7 +9582,7 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>132</v>
@@ -9629,19 +9629,19 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9653,7 +9653,7 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>89</v>
@@ -9681,13 +9681,13 @@
         <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>317</v>
@@ -9794,10 +9794,10 @@
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>163</v>
@@ -9901,13 +9901,13 @@
         <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>85</v>
@@ -10009,13 +10009,13 @@
         <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>147</v>
@@ -10117,13 +10117,13 @@
         <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>163</v>
@@ -10227,13 +10227,13 @@
         <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>303</v>
@@ -10450,7 +10450,7 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>132</v>
@@ -10497,19 +10497,19 @@
         <v>21</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10521,7 +10521,7 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>89</v>
@@ -10549,13 +10549,13 @@
         <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>317</v>
@@ -10662,10 +10662,10 @@
         <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>163</v>
@@ -10769,13 +10769,13 @@
         <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>85</v>
@@ -10877,13 +10877,13 @@
         <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>147</v>
@@ -10985,13 +10985,13 @@
         <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>163</v>
@@ -11097,13 +11097,13 @@
         <v>84</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>385</v>
@@ -11320,7 +11320,7 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>132</v>
@@ -11367,19 +11367,19 @@
         <v>21</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11391,7 +11391,7 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>89</v>
@@ -11419,13 +11419,13 @@
         <v>84</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>317</v>
@@ -11532,10 +11532,10 @@
         <v>21</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>163</v>
@@ -11639,13 +11639,13 @@
         <v>84</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>85</v>
@@ -11747,13 +11747,13 @@
         <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>147</v>
@@ -11855,13 +11855,13 @@
         <v>84</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>163</v>
@@ -11965,13 +11965,13 @@
         <v>84</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>401</v>
@@ -12075,13 +12075,13 @@
         <v>84</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>385</v>
@@ -12300,7 +12300,7 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>132</v>
@@ -12347,19 +12347,19 @@
         <v>21</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12371,7 +12371,7 @@
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>89</v>
@@ -12399,13 +12399,13 @@
         <v>84</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>317</v>
@@ -12512,10 +12512,10 @@
         <v>21</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>163</v>
@@ -12619,13 +12619,13 @@
         <v>84</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>85</v>
@@ -12727,13 +12727,13 @@
         <v>84</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>147</v>
@@ -12835,13 +12835,13 @@
         <v>84</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>163</v>
@@ -12947,13 +12947,13 @@
         <v>84</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>295</v>
@@ -13172,7 +13172,7 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>132</v>
@@ -13219,19 +13219,19 @@
         <v>21</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13243,7 +13243,7 @@
         <v>21</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>89</v>
@@ -13271,13 +13271,13 @@
         <v>84</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>303</v>
@@ -13494,7 +13494,7 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>132</v>
@@ -13541,19 +13541,19 @@
         <v>21</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13565,7 +13565,7 @@
         <v>21</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>89</v>
@@ -13593,13 +13593,13 @@
         <v>84</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>317</v>
@@ -13706,10 +13706,10 @@
         <v>21</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>163</v>
@@ -13813,13 +13813,13 @@
         <v>84</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
         <v>85</v>
@@ -13921,13 +13921,13 @@
         <v>84</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>147</v>
@@ -14029,13 +14029,13 @@
         <v>84</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>163</v>
@@ -14139,13 +14139,13 @@
         <v>84</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>303</v>
@@ -14362,7 +14362,7 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>132</v>
@@ -14409,19 +14409,19 @@
         <v>21</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -14433,7 +14433,7 @@
         <v>21</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>89</v>
@@ -14461,13 +14461,13 @@
         <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>317</v>
@@ -14574,10 +14574,10 @@
         <v>21</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>163</v>
@@ -14681,13 +14681,13 @@
         <v>84</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>85</v>
@@ -14789,13 +14789,13 @@
         <v>84</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>147</v>
@@ -14897,13 +14897,13 @@
         <v>84</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>163</v>
@@ -15009,13 +15009,13 @@
         <v>84</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>463</v>
@@ -15234,7 +15234,7 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>132</v>
@@ -15281,19 +15281,19 @@
         <v>21</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15305,7 +15305,7 @@
         <v>21</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>89</v>
@@ -15333,13 +15333,13 @@
         <v>84</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>468</v>
@@ -15554,7 +15554,7 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>132</v>
@@ -15601,19 +15601,19 @@
         <v>21</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15625,7 +15625,7 @@
         <v>21</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>89</v>
@@ -15653,13 +15653,13 @@
         <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>317</v>
@@ -15766,10 +15766,10 @@
         <v>21</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>163</v>
@@ -15873,13 +15873,13 @@
         <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
         <v>85</v>
@@ -15981,13 +15981,13 @@
         <v>84</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
         <v>147</v>
@@ -16089,13 +16089,13 @@
         <v>84</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>163</v>
@@ -16199,13 +16199,13 @@
         <v>84</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>468</v>
@@ -16420,7 +16420,7 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>132</v>
@@ -16467,19 +16467,19 @@
         <v>21</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -16491,7 +16491,7 @@
         <v>21</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>89</v>
@@ -16519,13 +16519,13 @@
         <v>84</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>317</v>
@@ -16632,10 +16632,10 @@
         <v>21</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>163</v>
@@ -16739,13 +16739,13 @@
         <v>84</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
         <v>85</v>
@@ -16847,13 +16847,13 @@
         <v>84</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
         <v>147</v>
@@ -16955,13 +16955,13 @@
         <v>84</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
         <v>163</v>
@@ -17065,13 +17065,13 @@
         <v>84</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
         <v>463</v>
@@ -17290,7 +17290,7 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>132</v>
@@ -17337,19 +17337,19 @@
         <v>21</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -17361,7 +17361,7 @@
         <v>21</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>89</v>
@@ -17389,13 +17389,13 @@
         <v>84</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>468</v>
@@ -17610,7 +17610,7 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L144" t="s" s="2">
         <v>132</v>
@@ -17657,19 +17657,19 @@
         <v>21</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -17681,7 +17681,7 @@
         <v>21</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>89</v>
@@ -17709,13 +17709,13 @@
         <v>84</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
         <v>317</v>
@@ -17822,10 +17822,10 @@
         <v>21</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>163</v>
@@ -17929,13 +17929,13 @@
         <v>84</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>85</v>
@@ -18037,13 +18037,13 @@
         <v>84</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>147</v>
@@ -18145,13 +18145,13 @@
         <v>84</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
         <v>163</v>
@@ -18255,13 +18255,13 @@
         <v>84</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>468</v>
@@ -18476,7 +18476,7 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L152" t="s" s="2">
         <v>132</v>
@@ -18523,19 +18523,19 @@
         <v>21</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
@@ -18547,7 +18547,7 @@
         <v>21</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>89</v>
@@ -18575,13 +18575,13 @@
         <v>84</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>317</v>
@@ -18688,10 +18688,10 @@
         <v>21</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
         <v>163</v>
@@ -18795,13 +18795,13 @@
         <v>84</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
         <v>85</v>
@@ -18903,13 +18903,13 @@
         <v>84</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
         <v>147</v>
@@ -19011,13 +19011,13 @@
         <v>84</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
         <v>163</v>
@@ -19121,13 +19121,13 @@
         <v>84</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>303</v>
@@ -19346,7 +19346,7 @@
         <v>21</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>132</v>
@@ -19393,19 +19393,19 @@
         <v>21</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC160" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -19417,7 +19417,7 @@
         <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>89</v>
@@ -19445,13 +19445,13 @@
         <v>84</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
         <v>317</v>
@@ -19558,10 +19558,10 @@
         <v>21</v>
       </c>
       <c r="I162" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K162" t="s" s="2">
         <v>163</v>
@@ -19665,13 +19665,13 @@
         <v>84</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>85</v>
@@ -19773,13 +19773,13 @@
         <v>84</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
         <v>147</v>
@@ -19881,13 +19881,13 @@
         <v>84</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
         <v>163</v>
@@ -19991,13 +19991,13 @@
         <v>84</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
         <v>303</v>
@@ -20214,7 +20214,7 @@
         <v>21</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L168" t="s" s="2">
         <v>132</v>
@@ -20261,19 +20261,19 @@
         <v>21</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -20285,7 +20285,7 @@
         <v>21</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>89</v>
@@ -20313,13 +20313,13 @@
         <v>84</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>317</v>
@@ -20426,10 +20426,10 @@
         <v>21</v>
       </c>
       <c r="I170" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
         <v>163</v>
@@ -20533,13 +20533,13 @@
         <v>84</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
         <v>85</v>
@@ -20641,13 +20641,13 @@
         <v>84</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
         <v>147</v>
@@ -20749,13 +20749,13 @@
         <v>84</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
         <v>163</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5957" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5957" uniqueCount="558">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -594,7 +594,7 @@
     <t>Dosage.additionalInstruction.text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -725,6 +725,9 @@
     <t>Dosage.site.text</t>
   </si>
   <si>
+    <t>Fachliche Begründung: TODO</t>
+  </si>
+  <si>
     <t>Dosage.route</t>
   </si>
   <si>
@@ -1202,7 +1205,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Amount of medication per dose</t>
   </si>
   <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
@@ -5797,7 +5800,7 @@
         <v>85</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>188</v>
@@ -5878,10 +5881,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5907,14 +5910,14 @@
         <v>120</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5942,10 +5945,10 @@
         <v>125</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5963,7 +5966,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5978,18 +5981,18 @@
         <v>81</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6092,10 +6095,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6200,10 +6203,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6310,10 +6313,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6416,10 +6419,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6524,10 +6527,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6572,7 +6575,7 @@
         <v>21</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>21</v>
@@ -6634,10 +6637,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6742,10 +6745,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6850,10 +6853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6958,10 +6961,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7068,10 +7071,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7097,7 +7100,7 @@
         <v>85</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>188</v>
@@ -7178,10 +7181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7207,16 +7210,16 @@
         <v>120</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7244,10 +7247,10 @@
         <v>125</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7265,7 +7268,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7280,18 +7283,18 @@
         <v>81</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7394,10 +7397,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7502,10 +7505,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7612,10 +7615,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7718,10 +7721,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7826,10 +7829,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7936,10 +7939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8044,10 +8047,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8152,10 +8155,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8260,10 +8263,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8370,10 +8373,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8399,7 +8402,7 @@
         <v>85</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>188</v>
@@ -8480,10 +8483,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8506,13 +8509,13 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8563,7 +8566,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8581,15 +8584,15 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8692,10 +8695,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8800,10 +8803,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8829,14 +8832,14 @@
         <v>120</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8864,10 +8867,10 @@
         <v>125</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8885,7 +8888,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8903,15 +8906,15 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8934,19 +8937,19 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -8983,17 +8986,17 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9008,21 +9011,21 @@
         <v>81</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>21</v>
@@ -9044,19 +9047,19 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9105,7 +9108,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9120,18 +9123,18 @@
         <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9234,10 +9237,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9342,10 +9345,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9368,16 +9371,16 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9427,7 +9430,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9439,21 +9442,21 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9556,10 +9559,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9664,10 +9667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9690,19 +9693,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9751,7 +9754,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9766,18 +9769,18 @@
         <v>81</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9803,20 +9806,20 @@
         <v>163</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R72" t="s" s="2">
         <v>21</v>
@@ -9837,13 +9840,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -9861,7 +9864,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9876,18 +9879,18 @@
         <v>81</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9913,14 +9916,14 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -9969,7 +9972,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9984,18 +9987,18 @@
         <v>81</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10021,14 +10024,14 @@
         <v>147</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10077,7 +10080,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10086,24 +10089,24 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10129,16 +10132,16 @@
         <v>163</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10187,7 +10190,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10202,18 +10205,18 @@
         <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10236,16 +10239,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10295,7 +10298,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10307,21 +10310,21 @@
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10424,10 +10427,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10532,10 +10535,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10558,19 +10561,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -10619,7 +10622,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10634,18 +10637,18 @@
         <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10671,20 +10674,20 @@
         <v>163</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>21</v>
@@ -10705,13 +10708,13 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
@@ -10729,7 +10732,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10744,18 +10747,18 @@
         <v>81</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10781,14 +10784,14 @@
         <v>85</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10837,7 +10840,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -10852,18 +10855,18 @@
         <v>81</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10889,14 +10892,14 @@
         <v>147</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -10945,7 +10948,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10954,24 +10957,24 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10997,16 +11000,16 @@
         <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11055,7 +11058,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11070,21 +11073,21 @@
         <v>81</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>21</v>
@@ -11106,19 +11109,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11143,11 +11146,11 @@
         <v>21</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -11165,7 +11168,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11180,18 +11183,18 @@
         <v>81</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11294,10 +11297,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11402,10 +11405,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11428,19 +11431,19 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -11489,7 +11492,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11504,18 +11507,18 @@
         <v>81</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11541,20 +11544,20 @@
         <v>163</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>21</v>
@@ -11575,13 +11578,13 @@
         <v>21</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -11599,7 +11602,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -11614,18 +11617,18 @@
         <v>81</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11651,14 +11654,14 @@
         <v>85</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -11707,7 +11710,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11722,18 +11725,18 @@
         <v>81</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11759,14 +11762,14 @@
         <v>147</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -11815,7 +11818,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11824,24 +11827,24 @@
         <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11867,16 +11870,16 @@
         <v>163</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -11925,7 +11928,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11940,18 +11943,18 @@
         <v>81</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11974,19 +11977,19 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -12023,17 +12026,17 @@
         <v>21</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12048,21 +12051,21 @@
         <v>81</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>21</v>
@@ -12084,19 +12087,19 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -12145,7 +12148,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12160,18 +12163,18 @@
         <v>81</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12274,10 +12277,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12382,10 +12385,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12408,19 +12411,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -12469,7 +12472,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -12484,18 +12487,18 @@
         <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12521,20 +12524,20 @@
         <v>163</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R97" t="s" s="2">
         <v>21</v>
@@ -12555,13 +12558,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -12579,7 +12582,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12594,18 +12597,18 @@
         <v>81</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12631,14 +12634,14 @@
         <v>85</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -12687,7 +12690,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12702,18 +12705,18 @@
         <v>81</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12739,14 +12742,14 @@
         <v>147</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -12795,7 +12798,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12804,24 +12807,24 @@
         <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12847,16 +12850,16 @@
         <v>163</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -12905,7 +12908,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12920,21 +12923,21 @@
         <v>81</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>21</v>
@@ -12956,19 +12959,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -13017,7 +13020,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13032,18 +13035,18 @@
         <v>81</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13146,10 +13149,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13254,10 +13257,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13280,16 +13283,16 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13339,7 +13342,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13351,21 +13354,21 @@
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13468,10 +13471,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13576,10 +13579,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13602,19 +13605,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -13663,7 +13666,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13678,18 +13681,18 @@
         <v>81</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13715,20 +13718,20 @@
         <v>163</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q108" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R108" t="s" s="2">
         <v>21</v>
@@ -13749,13 +13752,13 @@
         <v>21</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>21</v>
@@ -13773,7 +13776,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13788,18 +13791,18 @@
         <v>81</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13825,14 +13828,14 @@
         <v>85</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -13881,7 +13884,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -13896,18 +13899,18 @@
         <v>81</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13933,14 +13936,14 @@
         <v>147</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -13989,7 +13992,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13998,24 +14001,24 @@
         <v>84</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14041,16 +14044,16 @@
         <v>163</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>21</v>
@@ -14099,7 +14102,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14114,18 +14117,18 @@
         <v>81</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14148,16 +14151,16 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14207,7 +14210,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14219,21 +14222,21 @@
         <v>21</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14336,10 +14339,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14444,10 +14447,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14470,19 +14473,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -14531,7 +14534,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14546,18 +14549,18 @@
         <v>81</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14583,20 +14586,20 @@
         <v>163</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q116" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R116" t="s" s="2">
         <v>21</v>
@@ -14617,13 +14620,13 @@
         <v>21</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>21</v>
@@ -14641,7 +14644,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14656,18 +14659,18 @@
         <v>81</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14693,14 +14696,14 @@
         <v>85</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -14749,7 +14752,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14764,18 +14767,18 @@
         <v>81</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14801,14 +14804,14 @@
         <v>147</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -14857,7 +14860,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14866,24 +14869,24 @@
         <v>84</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14909,16 +14912,16 @@
         <v>163</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -14967,7 +14970,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -14982,21 +14985,21 @@
         <v>81</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>21</v>
@@ -15018,19 +15021,19 @@
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>21</v>
@@ -15079,7 +15082,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15094,18 +15097,18 @@
         <v>81</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15208,10 +15211,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15316,10 +15319,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15342,13 +15345,13 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -15399,7 +15402,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -15414,7 +15417,7 @@
         <v>81</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>21</v>
@@ -15422,10 +15425,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15528,10 +15531,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15636,10 +15639,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15662,19 +15665,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -15723,7 +15726,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -15738,18 +15741,18 @@
         <v>81</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15775,20 +15778,20 @@
         <v>163</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q127" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R127" t="s" s="2">
         <v>21</v>
@@ -15809,13 +15812,13 @@
         <v>21</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>21</v>
@@ -15833,7 +15836,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -15848,18 +15851,18 @@
         <v>81</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15885,14 +15888,14 @@
         <v>85</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -15941,7 +15944,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -15956,18 +15959,18 @@
         <v>81</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15993,14 +15996,14 @@
         <v>147</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -16049,7 +16052,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -16058,24 +16061,24 @@
         <v>84</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16101,16 +16104,16 @@
         <v>163</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -16159,7 +16162,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16174,18 +16177,18 @@
         <v>81</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16208,13 +16211,13 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -16265,7 +16268,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16280,7 +16283,7 @@
         <v>81</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>21</v>
@@ -16288,10 +16291,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16394,10 +16397,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16502,10 +16505,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16528,19 +16531,19 @@
         <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>21</v>
@@ -16589,7 +16592,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16604,18 +16607,18 @@
         <v>81</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16641,20 +16644,20 @@
         <v>163</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q135" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R135" t="s" s="2">
         <v>21</v>
@@ -16675,13 +16678,13 @@
         <v>21</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>21</v>
@@ -16699,7 +16702,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -16714,18 +16717,18 @@
         <v>81</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16751,14 +16754,14 @@
         <v>85</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>21</v>
@@ -16807,7 +16810,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -16822,18 +16825,18 @@
         <v>81</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16859,14 +16862,14 @@
         <v>147</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>21</v>
@@ -16915,7 +16918,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -16924,24 +16927,24 @@
         <v>84</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16967,16 +16970,16 @@
         <v>163</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>21</v>
@@ -17025,7 +17028,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17040,18 +17043,18 @@
         <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17074,19 +17077,19 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -17135,7 +17138,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17150,18 +17153,18 @@
         <v>81</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17264,10 +17267,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17372,10 +17375,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17398,13 +17401,13 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -17455,7 +17458,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -17470,7 +17473,7 @@
         <v>81</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>21</v>
@@ -17478,10 +17481,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17584,10 +17587,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17692,10 +17695,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17718,19 +17721,19 @@
         <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -17779,7 +17782,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -17794,18 +17797,18 @@
         <v>81</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17831,20 +17834,20 @@
         <v>163</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q146" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R146" t="s" s="2">
         <v>21</v>
@@ -17865,13 +17868,13 @@
         <v>21</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>21</v>
@@ -17889,7 +17892,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -17904,18 +17907,18 @@
         <v>81</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17941,14 +17944,14 @@
         <v>85</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>21</v>
@@ -17997,7 +18000,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -18012,18 +18015,18 @@
         <v>81</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18049,14 +18052,14 @@
         <v>147</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>21</v>
@@ -18105,7 +18108,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -18114,24 +18117,24 @@
         <v>84</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18157,16 +18160,16 @@
         <v>163</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>21</v>
@@ -18215,7 +18218,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -18230,18 +18233,18 @@
         <v>81</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18264,13 +18267,13 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -18321,7 +18324,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -18336,7 +18339,7 @@
         <v>81</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>21</v>
@@ -18344,10 +18347,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18450,10 +18453,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18558,10 +18561,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18584,19 +18587,19 @@
         <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>21</v>
@@ -18645,7 +18648,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -18660,18 +18663,18 @@
         <v>81</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18697,20 +18700,20 @@
         <v>163</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q154" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R154" t="s" s="2">
         <v>21</v>
@@ -18731,13 +18734,13 @@
         <v>21</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>21</v>
@@ -18755,7 +18758,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -18770,18 +18773,18 @@
         <v>81</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18807,14 +18810,14 @@
         <v>85</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>21</v>
@@ -18863,7 +18866,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -18878,18 +18881,18 @@
         <v>81</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18915,14 +18918,14 @@
         <v>147</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>21</v>
@@ -18971,7 +18974,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -18980,24 +18983,24 @@
         <v>84</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19023,16 +19026,16 @@
         <v>163</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>21</v>
@@ -19081,7 +19084,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -19096,18 +19099,18 @@
         <v>81</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19130,19 +19133,19 @@
         <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -19191,7 +19194,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -19203,10 +19206,10 @@
         <v>21</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>21</v>
@@ -19214,10 +19217,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19320,10 +19323,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19428,10 +19431,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19454,19 +19457,19 @@
         <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -19515,7 +19518,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -19530,18 +19533,18 @@
         <v>81</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19567,20 +19570,20 @@
         <v>163</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q162" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R162" t="s" s="2">
         <v>21</v>
@@ -19601,13 +19604,13 @@
         <v>21</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>21</v>
@@ -19625,7 +19628,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -19640,18 +19643,18 @@
         <v>81</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19677,14 +19680,14 @@
         <v>85</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -19733,7 +19736,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -19748,18 +19751,18 @@
         <v>81</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19785,14 +19788,14 @@
         <v>147</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>21</v>
@@ -19841,7 +19844,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -19850,24 +19853,24 @@
         <v>84</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19893,16 +19896,16 @@
         <v>163</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -19951,7 +19954,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -19966,18 +19969,18 @@
         <v>81</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20000,17 +20003,17 @@
         <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -20059,7 +20062,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -20071,10 +20074,10 @@
         <v>21</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>21</v>
@@ -20082,10 +20085,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20188,10 +20191,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20296,10 +20299,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20322,19 +20325,19 @@
         <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
@@ -20383,7 +20386,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -20398,18 +20401,18 @@
         <v>81</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20435,20 +20438,20 @@
         <v>163</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q170" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R170" t="s" s="2">
         <v>21</v>
@@ -20469,13 +20472,13 @@
         <v>21</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>21</v>
@@ -20493,7 +20496,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -20508,18 +20511,18 @@
         <v>81</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20545,14 +20548,14 @@
         <v>85</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -20601,7 +20604,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -20616,18 +20619,18 @@
         <v>81</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20653,14 +20656,14 @@
         <v>147</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -20709,7 +20712,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -20718,24 +20721,24 @@
         <v>84</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20761,16 +20764,16 @@
         <v>163</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -20819,7 +20822,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -20834,10 +20837,10 @@
         <v>81</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
